--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 3.088,91</t>
-  </si>
-  <si>
-    <t>36.1</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>4.54</t>
-  </si>
-  <si>
-    <t>18.8</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 3.086,12</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>4.55</t>
+  </si>
+  <si>
+    <t>18.7</t>
   </si>
   <si>
     <t>7.8</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>45.1%</t>
-  </si>
-  <si>
-    <t>19.6%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>45.0%</t>
+  </si>
+  <si>
+    <t>19.3%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -971,7 +971,7 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.3%</t>
+    <t>5.2%</t>
   </si>
   <si>
     <t>1.8%</t>
@@ -980,13 +980,13 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
   </si>
   <si>
     <t>967.0</t>
@@ -6785,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>2943.6700000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>49</v>
+      </c>
+      <c r="O36" s="6">
+        <v>31</v>
+      </c>
+      <c r="P36" s="7">
+        <v>5.8048155555555558</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>18.54032258064516</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.4682806451612898</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7667,7 +7725,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7697,35 +7755,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>2732.6700000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>34</v>
+      </c>
+      <c r="O42" s="6">
+        <v>27</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.0626272727272728</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>17.887037037037036</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.2771592592592595</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -935,22 +935,22 @@
     <t>214</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 3.086,12</t>
-  </si>
-  <si>
-    <t>36.2</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>4.55</t>
-  </si>
-  <si>
-    <t>18.7</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 3.077,28</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>4.56</t>
+  </si>
+  <si>
+    <t>18.8</t>
   </si>
   <si>
     <t>7.8</t>
@@ -959,10 +959,10 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>45.0%</t>
-  </si>
-  <si>
-    <t>19.3%</t>
+    <t>44.9%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -971,7 +971,7 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.2%</t>
+    <t>5.3%</t>
   </si>
   <si>
     <t>1.8%</t>
@@ -983,16 +983,16 @@
     <t>7.7%</t>
   </si>
   <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
-  </si>
-  <si>
-    <t>967.0</t>
-  </si>
-  <si>
-    <t>769.0</t>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>974.0</t>
+  </si>
+  <si>
+    <t>773.0</t>
   </si>
   <si>
     <t>63.0</t>
@@ -1001,22 +1001,22 @@
     <t>11.0</t>
   </si>
   <si>
-    <t>209.0</t>
-  </si>
-  <si>
-    <t>70.0</t>
+    <t>211.0</t>
+  </si>
+  <si>
+    <t>71.0</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>305.0</t>
-  </si>
-  <si>
-    <t>129.0</t>
-  </si>
-  <si>
-    <t>152.0</t>
+    <t>306.0</t>
+  </si>
+  <si>
+    <t>130.0</t>
+  </si>
+  <si>
+    <t>154.0</t>
   </si>
   <si>
     <t>0.8%</t>
@@ -16689,7 +16689,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16719,35 +16719,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>1485.5899999999999</v>
+      </c>
+      <c r="N102" s="6">
+        <v>19</v>
+      </c>
+      <c r="O102" s="6">
+        <v>12</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.3241649999999998</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>23.844441666666668</v>
+      </c>
+      <c r="R102" s="8">
+        <v>11.140909090909091</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -932,46 +932,49 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 3.077,28</t>
-  </si>
-  <si>
-    <t>36.1</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>4.56</t>
-  </si>
-  <si>
-    <t>18.8</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 3.087,33</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>22.2</t>
+  </si>
+  <si>
+    <t>4.59</t>
+  </si>
+  <si>
+    <t>18.7</t>
   </si>
   <si>
     <t>7.8</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>44.9%</t>
-  </si>
-  <si>
-    <t>19.4%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>44.6%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.3%</t>
+    <t>5.4%</t>
   </si>
   <si>
     <t>1.8%</t>
@@ -980,19 +983,19 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>974.0</t>
-  </si>
-  <si>
-    <t>773.0</t>
+    <t>8.1%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1059.0</t>
+  </si>
+  <si>
+    <t>835.0</t>
   </si>
   <si>
     <t>63.0</t>
@@ -1001,28 +1004,28 @@
     <t>11.0</t>
   </si>
   <si>
-    <t>211.0</t>
-  </si>
-  <si>
-    <t>71.0</t>
+    <t>224.0</t>
+  </si>
+  <si>
+    <t>74.0</t>
   </si>
   <si>
     <t>7.0</t>
   </si>
   <si>
-    <t>306.0</t>
-  </si>
-  <si>
-    <t>130.0</t>
-  </si>
-  <si>
-    <t>154.0</t>
+    <t>335.0</t>
+  </si>
+  <si>
+    <t>145.0</t>
+  </si>
+  <si>
+    <t>176.0</t>
   </si>
   <si>
     <t>0.8%</t>
   </si>
   <si>
-    <t>32.0</t>
+    <t>35.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6529,7 +6532,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6559,35 +6562,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>6315.8599999999997</v>
+      </c>
+      <c r="N34" s="6">
+        <v>88</v>
+      </c>
+      <c r="O34" s="6">
+        <v>71</v>
+      </c>
+      <c r="P34" s="7">
+        <v>10.521590909090909</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>18.465961971830986</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.8905477611940298</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.49295774647887325</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.54929577464788737</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.323943661971831</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.11267605633802817</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.22535211267605634</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>48</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>39</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>23</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>8</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -18735,33 +18796,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>14</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22448,7 +22555,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22478,35 +22585,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>1679.04</v>
+      </c>
+      <c r="N141" s="6">
+        <v>19</v>
+      </c>
+      <c r="O141" s="6">
+        <v>14</v>
+      </c>
+      <c r="P141" s="7">
+        <v>2.79</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>12.395235714285715</v>
+      </c>
+      <c r="R141" s="8">
+        <v>2.0384615384615383</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33263,137 +33428,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>36</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>27</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>6</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>2</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Z217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AA217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>336</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>337</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>338</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>338</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>339</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>339</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 3.087,33</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 3.093,75</t>
   </si>
   <si>
     <t>36.3</t>
@@ -950,7 +950,7 @@
     <t>22.2</t>
   </si>
   <si>
-    <t>4.59</t>
+    <t>4.60</t>
   </si>
   <si>
     <t>18.7</t>
@@ -962,7 +962,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>44.6%</t>
+    <t>44.7%</t>
   </si>
   <si>
     <t>20.2%</t>
@@ -25199,7 +25199,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25229,18 +25229,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>4266.8699999999999</v>
+      </c>
+      <c r="N159" s="6">
+        <v>47</v>
+      </c>
       <c r="O159" s="6">
         <v>32</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>6.1739130434782608</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>19.618749999999999</v>
+      </c>
+      <c r="R159" s="8">
+        <v>6.4144433333333337</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.1875</v>
+      </c>
       <c r="U159" s="9">
         <v>0.09375</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 3.093,75</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 3.089,25</t>
   </si>
   <si>
     <t>36.3</t>
@@ -962,7 +962,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>44.7%</t>
+    <t>44.8%</t>
   </si>
   <si>
     <t>20.2%</t>
@@ -14837,7 +14837,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14865,14 +14865,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>2262.3899999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>25</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.6794884615384618</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>17.849999999999998</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.3499999999999996</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.27272727272727271</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29157,7 +29169,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31811,7 +31823,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33444,7 +33456,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-05).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>27</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 3.089,25</t>
+    <t>R$ 3.060,02</t>
   </si>
   <si>
-    <t>36.3</t>
+    <t>35.9</t>
   </si>
   <si>
     <t>22.2</t>
   </si>
   <si>
-    <t>4.60</t>
+    <t>4.62</t>
   </si>
   <si>
-    <t>18.7</t>
+    <t>18.6</t>
   </si>
   <si>
-    <t>7.8</t>
+    <t>7.6</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
     <t>44.8%</t>
   </si>
   <si>
-    <t>20.2%</t>
+    <t>19.8%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -974,37 +974,37 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.3%</t>
   </si>
   <si>
-    <t>1.8%</t>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>8.1%</t>
+    <t>7.9%</t>
   </si>
   <si>
-    <t>3.5%</t>
+    <t>3.4%</t>
   </si>
   <si>
-    <t>4.3%</t>
+    <t>4.2%</t>
   </si>
   <si>
-    <t>1059.0</t>
+    <t>1064.0</t>
   </si>
   <si>
-    <t>835.0</t>
+    <t>840.0</t>
   </si>
   <si>
-    <t>63.0</t>
+    <t>64.0</t>
   </si>
   <si>
     <t>11.0</t>
   </si>
   <si>
-    <t>224.0</t>
+    <t>225.0</t>
   </si>
   <si>
     <t>74.0</t>
@@ -1013,13 +1013,13 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>335.0</t>
+    <t>336.0</t>
   </si>
   <si>
     <t>145.0</t>
   </si>
   <si>
-    <t>176.0</t>
+    <t>178.0</t>
   </si>
   <si>
     <t>0.8%</t>
@@ -9193,7 +9193,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9223,14 +9223,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>206.40000000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>2</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>7.0083500000000001</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>17.38335</v>
+      </c>
+      <c r="R51" s="8">
+        <v>3.4833500000000002</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10262,33 +10274,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>37</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.054054054054054057</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.054054054054054057</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24131,7 +24189,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24161,35 +24219,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2395.48</v>
+      </c>
+      <c r="N151" s="6">
+        <v>27</v>
+      </c>
+      <c r="O151" s="6">
+        <v>20</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.4265444444444446</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>14.711665</v>
+      </c>
+      <c r="R151" s="8">
+        <v>3.6100000000000003</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25013,7 +25129,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25043,35 +25159,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>1636.45</v>
+      </c>
+      <c r="N157" s="6">
+        <v>22</v>
+      </c>
+      <c r="O157" s="6">
+        <v>13</v>
+      </c>
+      <c r="P157" s="7">
+        <v>7.9464894736842115</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>17.839746153846153</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.0628230769230766</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25112,7 +25286,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25142,35 +25316,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>1919.6199999999999</v>
+      </c>
+      <c r="N158" s="6">
+        <v>23</v>
+      </c>
+      <c r="O158" s="6">
+        <v>18</v>
+      </c>
+      <c r="P158" s="7">
+        <v>3.8363636363636364</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>13.332405555555557</v>
+      </c>
+      <c r="R158" s="8">
+        <v>2.2907388888888889</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26095,7 +26327,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26125,35 +26357,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>3733.4899999999998</v>
+      </c>
+      <c r="N165" s="6">
+        <v>44</v>
+      </c>
+      <c r="O165" s="6">
+        <v>30</v>
+      </c>
+      <c r="P165" s="7">
+        <v>3.8511904761904763</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>12.051666666666668</v>
+      </c>
+      <c r="R165" s="8">
+        <v>0.84277666666666673</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
